--- a/Data/RemapDrafts/ShenheRemapDraft.xlsx
+++ b/Data/RemapDrafts/ShenheRemapDraft.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799BB872-8BFC-45B5-B45F-4C4AE77FFC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED85595D-0DB0-42F0-87AF-71C8A21B18FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" activeTab="1" xr2:uid="{3D0650C5-DBE0-4C90-9415-3AA816221020}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{3D0650C5-DBE0-4C90-9415-3AA816221020}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.4Shenhe to ShenheFrostFlower" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.4SheheFrostFlower to Shenhe" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.4Shenhe to ShenheFrostFlower" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.4SheheFrostFlower to Shenhe" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.4Shenhe to ShenheFrostFlower'!$A$1:$D$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.4Shenhe to ShenheFrostFlower'!$A$1:$D$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -187,13 +188,22 @@
   </si>
   <si>
     <t>Shenhe's neck</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +214,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -227,14 +253,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -587,17 +617,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07EE6DAC-AC6F-4A9A-910F-43B350F2C919}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{B1C6816D-86B5-45CC-B79C-3851CC43B9AD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2583E74-8F82-4F81-B04F-19E52E22920E}">
   <dimension ref="A1:D111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="81.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -611,7 +672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -622,7 +683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -633,7 +694,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -644,7 +705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -655,7 +716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -669,7 +730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -683,7 +744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -694,7 +755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -702,7 +763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -710,7 +771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -718,7 +779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -726,7 +787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -734,7 +795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -742,7 +803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -750,7 +811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -758,7 +819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -766,7 +827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -774,7 +835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -782,7 +843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -790,7 +851,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -798,7 +859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -806,7 +867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -814,7 +875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -822,7 +883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -830,7 +891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -838,7 +899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -852,7 +913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -866,7 +927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -880,7 +941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -891,7 +952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -902,7 +963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -913,7 +974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -924,7 +985,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -935,7 +996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -946,7 +1007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -957,7 +1018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -968,7 +1029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -979,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -990,7 +1051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1001,7 +1062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1012,7 +1073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1023,7 +1084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1034,7 +1095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1048,7 +1109,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1056,7 +1117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1064,7 +1125,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1075,7 +1136,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1086,7 +1147,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1097,7 +1158,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1108,7 +1169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1122,7 +1183,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1130,7 +1191,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1138,7 +1199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1146,7 +1207,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1160,7 +1221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1168,7 +1229,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1176,7 +1237,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1184,7 +1245,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1198,7 +1259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1212,7 +1273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1226,7 +1287,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1240,7 +1301,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1248,7 +1309,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1259,7 +1320,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1267,7 +1328,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1275,7 +1336,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1283,7 +1344,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1291,7 +1352,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1299,7 +1360,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1307,7 +1368,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1315,7 +1376,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1323,7 +1384,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1331,7 +1392,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1339,7 +1400,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1347,7 +1408,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1355,7 +1416,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1363,7 +1424,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1371,7 +1432,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1379,7 +1440,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1387,7 +1448,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1395,7 +1456,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1406,7 +1467,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1417,7 +1478,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1428,7 +1489,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1436,7 +1497,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1447,7 +1508,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1458,7 +1519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1466,7 +1527,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1474,7 +1535,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1482,7 +1543,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1490,7 +1551,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1498,7 +1559,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1506,7 +1567,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1514,7 +1575,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -1522,7 +1583,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -1530,7 +1591,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -1538,7 +1599,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -1546,7 +1607,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -1554,7 +1615,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -1562,7 +1623,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -1570,7 +1631,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -1578,7 +1639,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -1586,7 +1647,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -1594,7 +1655,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
@@ -1605,7 +1666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
@@ -1616,7 +1677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
@@ -1627,7 +1688,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
@@ -1635,7 +1696,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>107</v>
       </c>
@@ -1643,7 +1704,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>108</v>
       </c>
@@ -1651,7 +1712,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>109</v>
       </c>
@@ -1669,18 +1730,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{979D0712-8E47-4847-ADBC-0D4AB264156A}">
   <dimension ref="A1:D108"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="117.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="117.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1702,7 +1763,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1710,7 +1771,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1718,7 +1779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1726,7 +1787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1734,7 +1795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1742,7 +1803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1750,7 +1811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1758,7 +1819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1766,7 +1827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1774,7 +1835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1782,7 +1843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1790,7 +1851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1798,7 +1859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1806,7 +1867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1814,7 +1875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1822,7 +1883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1836,7 +1897,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1847,7 +1908,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1855,7 +1916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1863,7 +1924,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1871,7 +1932,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1879,7 +1940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1887,7 +1948,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1901,7 +1962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1912,7 +1973,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1920,7 +1981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1928,7 +1989,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1936,7 +1997,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1944,7 +2005,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1952,7 +2013,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1966,7 +2027,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1974,7 +2035,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1982,7 +2043,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1990,7 +2051,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1998,7 +2059,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2006,7 +2067,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2014,7 +2075,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2022,7 +2083,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2033,7 +2094,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2041,7 +2102,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2049,7 +2110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2057,7 +2118,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2065,7 +2126,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2076,7 +2137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2090,7 +2151,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2098,7 +2159,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2106,7 +2167,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2114,7 +2175,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2122,7 +2183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2133,7 +2194,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2144,7 +2205,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2155,7 +2216,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2166,7 +2227,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2177,7 +2238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2188,7 +2249,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2199,7 +2260,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2207,7 +2268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2215,7 +2276,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2223,7 +2284,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2231,7 +2292,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2239,7 +2300,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2247,7 +2308,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2255,7 +2316,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2263,7 +2324,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2271,7 +2332,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2279,7 +2340,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2287,7 +2348,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2295,7 +2356,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2303,7 +2364,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2311,7 +2372,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2319,7 +2380,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2327,7 +2388,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2335,7 +2396,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2343,7 +2404,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2351,7 +2412,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2359,7 +2420,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2367,7 +2428,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2375,7 +2436,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2383,7 +2444,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2391,7 +2452,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2399,7 +2460,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2407,7 +2468,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2415,7 +2476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2423,7 +2484,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2431,7 +2492,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2439,7 +2500,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2447,7 +2508,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2455,7 +2516,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2463,7 +2524,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2471,7 +2532,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2479,7 +2540,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2487,7 +2548,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2495,7 +2556,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -2503,7 +2564,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2511,7 +2572,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2519,7 +2580,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -2527,7 +2588,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2535,7 +2596,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2543,7 +2604,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -2551,7 +2612,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2559,7 +2620,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2567,7 +2628,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -2575,7 +2636,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2583,7 +2644,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2591,7 +2652,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
@@ -2599,7 +2660,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
